--- a/GenBOE/GenBOE.Tests/ActionLogic/Import/MOQ Table/MOQTableSSC_Valid.xlsx
+++ b/GenBOE/GenBOE.Tests/ActionLogic/Import/MOQ Table/MOQTableSSC_Valid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twilson3\Documents\Repos\IES\GenBOE\GenBOE.Tests\ActionLogic\Import\MOQ Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E522412-E138-4E2B-908E-F7374D67C4B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23864A51-6480-4345-8DDD-D0EC7BB09514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="1800" windowWidth="14715" windowHeight="11055" xr2:uid="{F2BDE59F-50D5-4F91-B73E-5DFBD476F53C}"/>
+    <workbookView xWindow="30585" yWindow="2205" windowWidth="21600" windowHeight="11385" xr2:uid="{F2BDE59F-50D5-4F91-B73E-5DFBD476F53C}"/>
   </bookViews>
   <sheets>
     <sheet name="MOQ Tables" sheetId="1" r:id="rId1"/>
@@ -168,9 +168,6 @@
     <t>WBS 2</t>
   </si>
   <si>
-    <t>5/2021</t>
-  </si>
-  <si>
     <t>FW 8/2021</t>
   </si>
   <si>
@@ -202,6 +199,9 @@
   </si>
   <si>
     <t>required cf 2</t>
+  </si>
+  <si>
+    <t>FW 5/2021</t>
   </si>
 </sst>
 </file>
@@ -732,10 +732,10 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -758,22 +758,22 @@
         <v>21</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J2" s="3">
         <v>100</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -796,22 +796,22 @@
         <v>22</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J3" s="3">
         <v>200</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/GenBOE/GenBOE.Tests/ActionLogic/Import/MOQ Table/MOQTableSSC_Valid.xlsx
+++ b/GenBOE/GenBOE.Tests/ActionLogic/Import/MOQ Table/MOQTableSSC_Valid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twilson3\Documents\Repos\IES\GenBOE\GenBOE.Tests\ActionLogic\Import\MOQ Table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twilson3\source\IES\GenBOE\GenBOE.Tests\ActionLogic\Import\MOQ Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23864A51-6480-4345-8DDD-D0EC7BB09514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5695AFEB-5495-41D1-A630-2EED715C9BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30585" yWindow="2205" windowWidth="21600" windowHeight="11385" xr2:uid="{F2BDE59F-50D5-4F91-B73E-5DFBD476F53C}"/>
+    <workbookView xWindow="23490" yWindow="60" windowWidth="19395" windowHeight="15480" xr2:uid="{F2BDE59F-50D5-4F91-B73E-5DFBD476F53C}"/>
   </bookViews>
   <sheets>
     <sheet name="MOQ Tables" sheetId="1" r:id="rId1"/>
@@ -126,9 +126,6 @@
     <t>Employee ID Filters</t>
   </si>
   <si>
-    <t>Total Relevant Hours After Employee ID Filters Applied</t>
-  </si>
-  <si>
     <t>Query Type</t>
   </si>
   <si>
@@ -202,6 +199,9 @@
   </si>
   <si>
     <t>FW 5/2021</t>
+  </si>
+  <si>
+    <t>Total Relevant Hours exclude unpaid (zero cost) hours and service centers, after application of Employee ID Filters</t>
   </si>
 </sst>
 </file>
@@ -387,9 +387,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -427,7 +427,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -533,7 +533,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -675,7 +675,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -729,89 +729,89 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J2" s="3">
         <v>100</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J3" s="3">
         <v>200</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -849,17 +849,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
